--- a/www/ig/fhir/tddui/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/www/ig/fhir/tddui/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T14:53:05+00:00</t>
+    <t>2026-03-16T15:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/www/ig/fhir/tddui/StructureDefinition-tddui-service-request-besoin.xlsx
+++ b/www/ig/fhir/tddui/StructureDefinition-tddui-service-request-besoin.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2841" uniqueCount="561">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:53:20+00:00</t>
+    <t>2026-07-22T14:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -512,7 +512,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant du besoin</t>
+    <t>Identifiers assigned to this order</t>
   </si>
   <si>
     <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
@@ -521,7 +521,8 @@
     <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
-    <t>idBesoin</t>
+    <t xml:space="preserve">pattern:type}
+</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -622,13 +623,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-service-request-identifier-besoin</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -650,9 +645,6 @@
   </si>
   <si>
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>https://identifiant-medicosocial-besoin.esante.gouv.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -736,6 +728,54 @@
   </si>
   <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin</t>
+  </si>
+  <si>
+    <t>idBesoin</t>
+  </si>
+  <si>
+    <t>Identifiant du besoin</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.use</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-service-request-identifier"/&gt;
+    &lt;code value="BES"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.system</t>
+  </si>
+  <si>
+    <t>https://identifiant-medicosocial-besoin.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.value</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ServiceRequestBesoinIdentifierFormat:l'identifiant du besoin doit respecter le format : 3+FINESS/identifiantLocalUsagerESSMS-BESO-numBesoin {value.matches('^3[0-9]{9}/[A-Za-z0-9]+-BESO-[A-Za-z0-9]+$')}</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.period</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idBesoin.assigner</t>
   </si>
   <si>
     <t>ServiceRequest.instantiatesCanonical</t>
@@ -2026,10 +2066,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:AP74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.8125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.69921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3410,7 +3450,7 @@
         <v>92</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3469,16 +3509,14 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>157</v>
@@ -3496,7 +3534,7 @@
         <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>163</v>
@@ -3939,31 +3977,29 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3984,7 +4020,7 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>188</v>
@@ -3998,10 +4034,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4009,7 +4045,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>92</v>
@@ -4027,16 +4063,16 @@
         <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4046,10 +4082,10 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4085,7 +4121,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4106,10 +4142,10 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4120,10 +4156,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4131,7 +4167,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>92</v>
@@ -4149,13 +4185,13 @@
         <v>169</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4169,7 +4205,7 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4205,7 +4241,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4226,10 +4262,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4240,10 +4276,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4266,13 +4302,13 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4323,7 +4359,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4344,10 +4380,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4358,10 +4394,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4384,16 +4420,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4443,7 +4479,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4464,10 +4500,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4478,21 +4514,23 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4504,16 +4542,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>234</v>
+        <v>158</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
+        <v>160</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>237</v>
+        <v>161</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4563,7 +4601,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>157</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4578,30 +4616,30 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>238</v>
+        <v>163</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4612,7 +4650,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4621,20 +4659,18 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4683,31 +4719,31 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4718,21 +4754,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4741,18 +4777,20 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>175</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4789,19 +4827,19 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4813,19 +4851,19 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>173</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4836,42 +4874,46 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>179</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4895,13 +4937,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4919,13 +4961,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>187</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -4937,13 +4979,13 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>135</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>188</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4954,18 +4996,18 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>92</v>
@@ -4980,19 +5022,19 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>265</v>
+        <v>191</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
+        <v>192</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5002,7 +5044,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -5017,13 +5059,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5041,7 +5081,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5059,13 +5099,13 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5076,10 +5116,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5096,24 +5136,26 @@
         <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
+        <v>200</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5122,10 +5164,10 @@
         <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>82</v>
@@ -5137,13 +5179,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5161,10 +5203,10 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>92</v>
@@ -5179,27 +5221,27 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5216,22 +5258,22 @@
         <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>285</v>
+        <v>209</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>286</v>
+        <v>210</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5245,7 +5287,7 @@
         <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>82</v>
@@ -5257,13 +5299,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5281,10 +5323,10 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>92</v>
@@ -5293,22 +5335,22 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5316,10 +5358,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>292</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5342,20 +5384,16 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5379,11 +5417,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5401,13 +5441,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>292</v>
+        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5416,19 +5456,19 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>299</v>
+        <v>220</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5436,10 +5476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5462,22 +5502,22 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>223</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q29" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5497,13 +5537,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5521,7 +5561,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>227</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5539,16 +5579,16 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>309</v>
+        <v>229</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5556,10 +5596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5570,38 +5610,34 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>312</v>
+        <v>245</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>313</v>
+        <v>246</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q30" t="s" s="2">
-        <v>317</v>
-      </c>
+      <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5645,13 +5681,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5663,13 +5699,13 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>318</v>
+        <v>249</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>319</v>
+        <v>251</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5680,21 +5716,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5706,16 +5742,16 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>322</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>323</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>324</v>
+        <v>255</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5741,13 +5777,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5765,13 +5801,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5783,35 +5819,35 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>328</v>
+        <v>256</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>329</v>
+        <v>250</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>330</v>
+        <v>251</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>92</v>
@@ -5823,16 +5859,16 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>169</v>
+        <v>259</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>171</v>
+        <v>261</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5883,31 +5919,31 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5918,14 +5954,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>334</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>151</v>
+        <v>267</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5941,20 +5977,18 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>268</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5991,19 +6025,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6015,19 +6049,19 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6038,21 +6072,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6064,19 +6098,19 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>336</v>
+        <v>158</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>340</v>
+        <v>279</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6125,13 +6159,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>341</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6143,13 +6177,13 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>343</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6160,10 +6194,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6180,26 +6214,24 @@
         <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>345</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>346</v>
+        <v>285</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6223,13 +6255,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6247,10 +6279,10 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>92</v>
@@ -6262,62 +6294,62 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>351</v>
+        <v>290</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>352</v>
+        <v>291</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>355</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>356</v>
+        <v>296</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>357</v>
+        <v>297</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6343,13 +6375,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>325</v>
+        <v>184</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>359</v>
+        <v>299</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6367,16 +6399,16 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6385,27 +6417,27 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>361</v>
+        <v>135</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>362</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>362</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6425,19 +6457,23 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>170</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6461,13 +6497,11 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6485,34 +6519,34 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>172</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>173</v>
+        <v>311</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6520,21 +6554,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6543,25 +6577,25 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>175</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q38" s="2"/>
+      <c r="Q38" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="R38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6581,58 +6615,58 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>178</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>173</v>
+        <v>320</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6640,10 +6674,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>364</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>364</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6654,36 +6688,38 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q39" s="2"/>
+      <c r="Q39" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="R39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6727,13 +6763,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6745,13 +6781,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6762,18 +6798,18 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>92</v>
@@ -6788,20 +6824,18 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6825,13 +6859,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6849,7 +6883,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6864,30 +6898,30 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6907,21 +6941,19 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>169</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>170</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>171</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6969,7 +7001,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>172</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6981,7 +7013,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6990,10 +7022,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>372</v>
+        <v>173</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7004,21 +7036,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7027,18 +7059,20 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>374</v>
+        <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>375</v>
+        <v>175</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7075,68 +7109,68 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>178</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>379</v>
+        <v>173</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7148,16 +7182,20 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7205,13 +7243,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7223,35 +7261,35 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>92</v>
@@ -7266,16 +7304,20 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>394</v>
+        <v>169</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7323,7 +7365,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7338,41 +7380,41 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>399</v>
+        <v>363</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>402</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>402</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7384,15 +7426,17 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>403</v>
+        <v>190</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7417,13 +7461,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7441,16 +7485,16 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>402</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7462,28 +7506,28 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>408</v>
+        <v>341</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>409</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7499,16 +7543,16 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>412</v>
+        <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>413</v>
+        <v>170</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>414</v>
+        <v>171</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7559,7 +7603,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>172</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7571,44 +7615,44 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>417</v>
+        <v>173</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>421</v>
+        <v>151</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7617,19 +7661,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>175</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>424</v>
+        <v>176</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>425</v>
+        <v>154</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7667,68 +7711,68 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>420</v>
+        <v>178</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>428</v>
+        <v>173</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7740,18 +7784,20 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>347</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>348</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
+        <v>349</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7775,13 +7821,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7799,13 +7845,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -7817,16 +7863,16 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>439</v>
+        <v>353</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>440</v>
+        <v>354</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7834,21 +7880,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7860,18 +7906,20 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>444</v>
+        <v>169</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>445</v>
+        <v>356</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>446</v>
+        <v>357</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7919,13 +7967,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>360</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7934,19 +7982,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>449</v>
+        <v>362</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7954,10 +8002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>451</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>451</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7968,7 +8016,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7980,16 +8028,18 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>379</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>452</v>
+        <v>380</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>453</v>
+        <v>381</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8013,13 +8063,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8037,13 +8087,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>451</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8058,13 +8108,13 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>456</v>
+        <v>383</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8072,10 +8122,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>457</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>457</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8083,10 +8133,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8098,13 +8148,13 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>458</v>
+        <v>385</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>452</v>
+        <v>386</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>459</v>
+        <v>387</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8155,13 +8205,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>457</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8173,38 +8223,38 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>460</v>
+        <v>390</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>393</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8216,17 +8266,15 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8251,13 +8299,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8275,13 +8323,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8293,38 +8341,38 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>467</v>
+        <v>398</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>468</v>
+        <v>399</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>470</v>
+        <v>401</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>471</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>471</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8336,17 +8384,15 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>472</v>
+        <v>405</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>473</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8395,13 +8441,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>471</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8413,27 +8459,27 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>476</v>
+        <v>408</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>477</v>
+        <v>409</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>478</v>
+        <v>410</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>470</v>
+        <v>411</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>479</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>479</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8444,7 +8490,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8453,16 +8499,16 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>482</v>
+        <v>416</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8489,13 +8535,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8513,13 +8559,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>479</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8531,38 +8577,38 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>485</v>
+        <v>419</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>486</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>486</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>487</v>
+        <v>422</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8571,20 +8617,18 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>488</v>
+        <v>423</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>489</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8633,13 +8677,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>486</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8651,38 +8695,38 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>492</v>
+        <v>426</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>494</v>
+        <v>428</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8694,16 +8738,16 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>496</v>
+        <v>433</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>497</v>
+        <v>434</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>498</v>
+        <v>435</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>499</v>
+        <v>436</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8753,13 +8797,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>495</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8771,38 +8815,38 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>500</v>
+        <v>438</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>501</v>
+        <v>439</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8817,17 +8861,15 @@
         <v>190</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>504</v>
+        <v>444</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8851,13 +8893,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>508</v>
+        <v>447</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>509</v>
+        <v>448</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8875,13 +8917,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -8893,31 +8935,31 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>510</v>
+        <v>451</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8933,18 +8975,20 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>513</v>
+        <v>455</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>50</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8993,7 +9037,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9011,27 +9055,27 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>515</v>
+        <v>459</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>361</v>
+        <v>460</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>516</v>
+        <v>461</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>518</v>
+        <v>462</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>518</v>
+        <v>462</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9042,7 +9086,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9051,16 +9095,16 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>170</v>
+        <v>463</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>171</v>
+        <v>464</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9087,13 +9131,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9111,19 +9155,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>172</v>
+        <v>462</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9135,10 +9179,10 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>173</v>
+        <v>467</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9146,14 +9190,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>519</v>
+        <v>468</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>519</v>
+        <v>468</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9169,20 +9213,18 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>137</v>
+        <v>469</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>175</v>
+        <v>463</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9219,19 +9261,19 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>178</v>
+        <v>468</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9243,7 +9285,7 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9255,10 +9297,10 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>173</v>
+        <v>471</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9266,10 +9308,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>472</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>472</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9280,7 +9322,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9292,16 +9334,16 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>521</v>
+        <v>190</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>522</v>
+        <v>473</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>523</v>
+        <v>474</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>524</v>
+        <v>475</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9327,13 +9369,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9351,13 +9393,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>525</v>
+        <v>472</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9369,16 +9411,16 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>135</v>
+        <v>479</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>526</v>
+        <v>480</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9386,10 +9428,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9400,7 +9442,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9412,15 +9454,17 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>412</v>
+        <v>483</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9469,13 +9513,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>530</v>
+        <v>482</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9487,16 +9531,16 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>531</v>
+        <v>489</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -9504,10 +9548,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>532</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>532</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9515,10 +9559,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9527,16 +9571,16 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>533</v>
+        <v>491</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>534</v>
+        <v>492</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>535</v>
+        <v>493</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9587,13 +9631,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>536</v>
+        <v>490</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9602,16 +9646,16 @@
         <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>135</v>
+        <v>495</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>538</v>
+        <v>496</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9622,21 +9666,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9645,18 +9689,20 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>169</v>
+        <v>499</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9705,13 +9751,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9723,13 +9769,13 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>361</v>
+        <v>504</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>542</v>
+        <v>505</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9740,10 +9786,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9763,19 +9809,19 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>545</v>
+        <v>508</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>547</v>
+        <v>510</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9825,7 +9871,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9843,18 +9889,1090 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK72" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AO65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP65" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>82</v>
       </c>
     </row>
